--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -3917,7 +3917,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D305"/>
+  <dimension ref="A1:D509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -9404,210 +9404,3270 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="306" ht="18.75" customHeight="1"/>
-    <row r="307" ht="18.75" customHeight="1"/>
-    <row r="308" ht="18.75" customHeight="1"/>
-    <row r="309" ht="18.75" customHeight="1"/>
-    <row r="310" ht="18.75" customHeight="1"/>
-    <row r="311" ht="18.75" customHeight="1"/>
-    <row r="312" ht="18.75" customHeight="1"/>
-    <row r="313" ht="18.75" customHeight="1"/>
-    <row r="314" ht="18.75" customHeight="1"/>
-    <row r="315" ht="18.75" customHeight="1"/>
-    <row r="316" ht="18.75" customHeight="1"/>
-    <row r="317" ht="18.75" customHeight="1"/>
-    <row r="318" ht="18.75" customHeight="1"/>
-    <row r="319" ht="18.75" customHeight="1"/>
-    <row r="320" ht="18.75" customHeight="1"/>
-    <row r="321" ht="18.75" customHeight="1"/>
-    <row r="322" ht="18.75" customHeight="1"/>
-    <row r="323" ht="18.75" customHeight="1"/>
-    <row r="324" ht="18.75" customHeight="1"/>
-    <row r="325" ht="18.75" customHeight="1"/>
-    <row r="326" ht="18.75" customHeight="1"/>
-    <row r="327" ht="18.75" customHeight="1"/>
-    <row r="328" ht="18.75" customHeight="1"/>
-    <row r="329" ht="18.75" customHeight="1"/>
-    <row r="330" ht="18.75" customHeight="1"/>
-    <row r="331" ht="18.75" customHeight="1"/>
-    <row r="332" ht="18.75" customHeight="1"/>
-    <row r="333" ht="18.75" customHeight="1"/>
-    <row r="334" ht="18.75" customHeight="1"/>
-    <row r="335" ht="18.75" customHeight="1"/>
-    <row r="336" ht="18.75" customHeight="1"/>
-    <row r="337" ht="18.75" customHeight="1"/>
-    <row r="338" ht="18.75" customHeight="1"/>
-    <row r="339" ht="18.75" customHeight="1"/>
-    <row r="340" ht="18.75" customHeight="1"/>
-    <row r="341" ht="18.75" customHeight="1"/>
-    <row r="342" ht="18.75" customHeight="1"/>
-    <row r="343" ht="18.75" customHeight="1"/>
-    <row r="344" ht="18.75" customHeight="1"/>
-    <row r="345" ht="18.75" customHeight="1"/>
-    <row r="346" ht="18.75" customHeight="1"/>
-    <row r="347" ht="18.75" customHeight="1"/>
-    <row r="348" ht="18.75" customHeight="1"/>
-    <row r="349" ht="18.75" customHeight="1"/>
-    <row r="350" ht="18.75" customHeight="1"/>
-    <row r="351" ht="18.75" customHeight="1"/>
-    <row r="352" ht="18.75" customHeight="1"/>
-    <row r="353" ht="18.75" customHeight="1"/>
-    <row r="354" ht="18.75" customHeight="1"/>
-    <row r="355" ht="18.75" customHeight="1"/>
-    <row r="356" ht="18.75" customHeight="1"/>
-    <row r="357" ht="18.75" customHeight="1"/>
-    <row r="358" ht="18.75" customHeight="1"/>
-    <row r="359" ht="18.75" customHeight="1"/>
-    <row r="360" ht="18.75" customHeight="1"/>
-    <row r="361" ht="18.75" customHeight="1"/>
-    <row r="362" ht="18.75" customHeight="1"/>
-    <row r="363" ht="18.75" customHeight="1"/>
-    <row r="364" ht="18.75" customHeight="1"/>
-    <row r="365" ht="18.75" customHeight="1"/>
-    <row r="366" ht="18.75" customHeight="1"/>
-    <row r="367" ht="18.75" customHeight="1"/>
-    <row r="368" ht="18.75" customHeight="1"/>
-    <row r="369" ht="18.75" customHeight="1"/>
-    <row r="370" ht="18.75" customHeight="1"/>
-    <row r="371" ht="18.75" customHeight="1"/>
-    <row r="372" ht="18.75" customHeight="1"/>
-    <row r="373" ht="18.75" customHeight="1"/>
-    <row r="374" ht="18.75" customHeight="1"/>
-    <row r="375" ht="18.75" customHeight="1"/>
-    <row r="376" ht="18.75" customHeight="1"/>
-    <row r="377" ht="18.75" customHeight="1"/>
-    <row r="378" ht="18.75" customHeight="1"/>
-    <row r="379" ht="18.75" customHeight="1"/>
-    <row r="380" ht="18.75" customHeight="1"/>
-    <row r="381" ht="18.75" customHeight="1"/>
-    <row r="382" ht="18.75" customHeight="1"/>
-    <row r="383" ht="18.75" customHeight="1"/>
-    <row r="384" ht="18.75" customHeight="1"/>
-    <row r="385" ht="18.75" customHeight="1"/>
-    <row r="386" ht="18.75" customHeight="1"/>
-    <row r="387" ht="18.75" customHeight="1"/>
-    <row r="388" ht="18.75" customHeight="1"/>
-    <row r="389" ht="18.75" customHeight="1"/>
-    <row r="390" ht="18.75" customHeight="1"/>
-    <row r="391" ht="18.75" customHeight="1"/>
-    <row r="392" ht="18.75" customHeight="1"/>
-    <row r="393" ht="18.75" customHeight="1"/>
-    <row r="394" ht="18.75" customHeight="1"/>
-    <row r="395" ht="18.75" customHeight="1"/>
-    <row r="396" ht="18.75" customHeight="1"/>
-    <row r="397" ht="18.75" customHeight="1"/>
-    <row r="398" ht="18.75" customHeight="1"/>
-    <row r="399" ht="18.75" customHeight="1"/>
-    <row r="400" ht="18.75" customHeight="1"/>
-    <row r="401" ht="18.75" customHeight="1"/>
-    <row r="402" ht="18.75" customHeight="1"/>
-    <row r="403" ht="18.75" customHeight="1"/>
-    <row r="404" ht="18.75" customHeight="1"/>
-    <row r="405" ht="18.75" customHeight="1"/>
-    <row r="406" ht="18.75" customHeight="1"/>
-    <row r="407" ht="18.75" customHeight="1"/>
-    <row r="408" ht="18.75" customHeight="1"/>
-    <row r="409" ht="18.75" customHeight="1"/>
-    <row r="410" ht="18.75" customHeight="1"/>
-    <row r="411" ht="18.75" customHeight="1"/>
-    <row r="412" ht="18.75" customHeight="1"/>
-    <row r="413" ht="18.75" customHeight="1"/>
-    <row r="414" ht="18.75" customHeight="1"/>
-    <row r="415" ht="18.75" customHeight="1"/>
-    <row r="416" ht="18.75" customHeight="1"/>
-    <row r="417" ht="18.75" customHeight="1"/>
-    <row r="418" ht="18.75" customHeight="1"/>
-    <row r="419" ht="18.75" customHeight="1"/>
-    <row r="420" ht="18.75" customHeight="1"/>
-    <row r="421" ht="18.75" customHeight="1"/>
-    <row r="422" ht="18.75" customHeight="1"/>
-    <row r="423" ht="18.75" customHeight="1"/>
-    <row r="424" ht="18.75" customHeight="1"/>
-    <row r="425" ht="18.75" customHeight="1"/>
-    <row r="426" ht="18.75" customHeight="1"/>
-    <row r="427" ht="18.75" customHeight="1"/>
-    <row r="428" ht="18.75" customHeight="1"/>
-    <row r="429" ht="18.75" customHeight="1"/>
-    <row r="430" ht="18.75" customHeight="1"/>
-    <row r="431" ht="18.75" customHeight="1"/>
-    <row r="432" ht="18.75" customHeight="1"/>
-    <row r="433" ht="18.75" customHeight="1"/>
-    <row r="434" ht="18.75" customHeight="1"/>
-    <row r="435" ht="18.75" customHeight="1"/>
-    <row r="436" ht="18.75" customHeight="1"/>
-    <row r="437" ht="18.75" customHeight="1"/>
-    <row r="438" ht="18.75" customHeight="1"/>
-    <row r="439" ht="18.75" customHeight="1"/>
-    <row r="440" ht="18.75" customHeight="1"/>
-    <row r="441" ht="18.75" customHeight="1"/>
-    <row r="442" ht="18.75" customHeight="1"/>
-    <row r="443" ht="18.75" customHeight="1"/>
-    <row r="444" ht="18.75" customHeight="1"/>
-    <row r="445" ht="18.75" customHeight="1"/>
-    <row r="446" ht="18.75" customHeight="1"/>
-    <row r="447" ht="18.75" customHeight="1"/>
-    <row r="448" ht="18.75" customHeight="1"/>
-    <row r="449" ht="18.75" customHeight="1"/>
-    <row r="450" ht="18.75" customHeight="1"/>
-    <row r="451" ht="18.75" customHeight="1"/>
-    <row r="452" ht="18.75" customHeight="1"/>
-    <row r="453" ht="18.75" customHeight="1"/>
-    <row r="454" ht="18.75" customHeight="1"/>
-    <row r="455" ht="18.75" customHeight="1"/>
-    <row r="456" ht="18.75" customHeight="1"/>
-    <row r="457" ht="18.75" customHeight="1"/>
-    <row r="458" ht="18.75" customHeight="1"/>
-    <row r="459" ht="18.75" customHeight="1"/>
-    <row r="460" ht="18.75" customHeight="1"/>
-    <row r="461" ht="18.75" customHeight="1"/>
-    <row r="462" ht="18.75" customHeight="1"/>
-    <row r="463" ht="18.75" customHeight="1"/>
-    <row r="464" ht="18.75" customHeight="1"/>
-    <row r="465" ht="18.75" customHeight="1"/>
-    <row r="466" ht="18.75" customHeight="1"/>
-    <row r="467" ht="18.75" customHeight="1"/>
-    <row r="468" ht="18.75" customHeight="1"/>
-    <row r="469" ht="18.75" customHeight="1"/>
-    <row r="470" ht="18.75" customHeight="1"/>
-    <row r="471" ht="18.75" customHeight="1"/>
-    <row r="472" ht="18.75" customHeight="1"/>
-    <row r="473" ht="18.75" customHeight="1"/>
-    <row r="474" ht="18.75" customHeight="1"/>
-    <row r="475" ht="18.75" customHeight="1"/>
-    <row r="476" ht="18.75" customHeight="1"/>
-    <row r="477" ht="18.75" customHeight="1"/>
-    <row r="478" ht="18.75" customHeight="1"/>
-    <row r="479" ht="18.75" customHeight="1"/>
-    <row r="480" ht="18.75" customHeight="1"/>
-    <row r="481" ht="18.75" customHeight="1"/>
-    <row r="482" ht="18.75" customHeight="1"/>
-    <row r="483" ht="18.75" customHeight="1"/>
-    <row r="484" ht="18.75" customHeight="1"/>
-    <row r="485" ht="18.75" customHeight="1"/>
-    <row r="486" ht="18.75" customHeight="1"/>
-    <row r="487" ht="18.75" customHeight="1"/>
-    <row r="488" ht="18.75" customHeight="1"/>
-    <row r="489" ht="18.75" customHeight="1"/>
-    <row r="490" ht="18.75" customHeight="1"/>
-    <row r="491" ht="18.75" customHeight="1"/>
-    <row r="492" ht="18.75" customHeight="1"/>
-    <row r="493" ht="18.75" customHeight="1"/>
-    <row r="494" ht="18.75" customHeight="1"/>
-    <row r="495" ht="18.75" customHeight="1"/>
-    <row r="496" ht="18.75" customHeight="1"/>
-    <row r="497" ht="18.75" customHeight="1"/>
-    <row r="498" ht="18.75" customHeight="1"/>
-    <row r="499" ht="18.75" customHeight="1"/>
-    <row r="500" ht="18.75" customHeight="1"/>
-    <row r="501" ht="18.75" customHeight="1"/>
-    <row r="502" ht="18.75" customHeight="1"/>
-    <row r="503" ht="18.75" customHeight="1"/>
-    <row r="504" ht="18.75" customHeight="1"/>
-    <row r="505" ht="18.75" customHeight="1"/>
-    <row r="506" ht="18.75" customHeight="1"/>
-    <row r="507" ht="18.75" customHeight="1"/>
-    <row r="508" ht="18.75" customHeight="1"/>
-    <row r="509" ht="18.75" customHeight="1"/>
+    <row r="306" ht="18.75" customHeight="1">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B306" s="22" t="n">
+        <v>38168</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0</v>
+      </c>
+      <c r="D306" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="307" ht="18.75" customHeight="1">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B307" s="22" t="n">
+        <v>38351</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0</v>
+      </c>
+      <c r="D307" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="308" ht="18.75" customHeight="1">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B308" s="22" t="n">
+        <v>38533</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0</v>
+      </c>
+      <c r="D308" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="309" ht="18.75" customHeight="1">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B309" s="22" t="n">
+        <v>38716</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0</v>
+      </c>
+      <c r="D309" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="310" ht="18.75" customHeight="1">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B310" s="22" t="n">
+        <v>38898</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0</v>
+      </c>
+      <c r="D310" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="311" ht="18.75" customHeight="1">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B311" s="22" t="n">
+        <v>39081</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0</v>
+      </c>
+      <c r="D311" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="312" ht="18.75" customHeight="1">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B312" s="22" t="n">
+        <v>39263</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0</v>
+      </c>
+      <c r="D312" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="313" ht="18.75" customHeight="1">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B313" s="22" t="n">
+        <v>39446</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0</v>
+      </c>
+      <c r="D313" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="314" ht="18.75" customHeight="1">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B314" s="22" t="n">
+        <v>39629</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0</v>
+      </c>
+      <c r="D314" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="315" ht="18.75" customHeight="1">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B315" s="22" t="n">
+        <v>39812</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0</v>
+      </c>
+      <c r="D315" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="316" ht="18.75" customHeight="1">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B316" s="22" t="n">
+        <v>39994</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0</v>
+      </c>
+      <c r="D316" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="317" ht="18.75" customHeight="1">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B317" s="22" t="n">
+        <v>40177</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0</v>
+      </c>
+      <c r="D317" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="318" ht="18.75" customHeight="1">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B318" s="22" t="n">
+        <v>40359</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0</v>
+      </c>
+      <c r="D318" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="319" ht="18.75" customHeight="1">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B319" s="22" t="n">
+        <v>40542</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0</v>
+      </c>
+      <c r="D319" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="320" ht="18.75" customHeight="1">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B320" s="22" t="n">
+        <v>40724</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0</v>
+      </c>
+      <c r="D320" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="321" ht="18.75" customHeight="1">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B321" s="22" t="n">
+        <v>40907</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0</v>
+      </c>
+      <c r="D321" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="322" ht="18.75" customHeight="1">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B322" s="22" t="n">
+        <v>41090</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0</v>
+      </c>
+      <c r="D322" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="323" ht="18.75" customHeight="1">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B323" s="22" t="n">
+        <v>41273</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0</v>
+      </c>
+      <c r="D323" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="324" ht="18.75" customHeight="1">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B324" s="22" t="n">
+        <v>41455</v>
+      </c>
+      <c r="C324" t="n">
+        <v>0</v>
+      </c>
+      <c r="D324" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="325" ht="18.75" customHeight="1">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B325" s="22" t="n">
+        <v>41638</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0</v>
+      </c>
+      <c r="D325" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="326" ht="18.75" customHeight="1">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B326" s="22" t="n">
+        <v>41820</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0</v>
+      </c>
+      <c r="D326" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="327" ht="18.75" customHeight="1">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B327" s="22" t="n">
+        <v>42003</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0</v>
+      </c>
+      <c r="D327" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="328" ht="18.75" customHeight="1">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B328" s="22" t="n">
+        <v>42185</v>
+      </c>
+      <c r="C328" t="n">
+        <v>0</v>
+      </c>
+      <c r="D328" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="329" ht="18.75" customHeight="1">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B329" s="22" t="n">
+        <v>42368</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0</v>
+      </c>
+      <c r="D329" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="330" ht="18.75" customHeight="1">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B330" s="22" t="n">
+        <v>42551</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0</v>
+      </c>
+      <c r="D330" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="331" ht="18.75" customHeight="1">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B331" s="22" t="n">
+        <v>42734</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0</v>
+      </c>
+      <c r="D331" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="332" ht="18.75" customHeight="1">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B332" s="22" t="n">
+        <v>42916</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0</v>
+      </c>
+      <c r="D332" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="333" ht="18.75" customHeight="1">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B333" s="22" t="n">
+        <v>43099</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0</v>
+      </c>
+      <c r="D333" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="334" ht="18.75" customHeight="1">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B334" s="22" t="n">
+        <v>43281</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0</v>
+      </c>
+      <c r="D334" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="335" ht="18.75" customHeight="1">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B335" s="22" t="n">
+        <v>43464</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0</v>
+      </c>
+      <c r="D335" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="336" ht="18.75" customHeight="1">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B336" s="22" t="n">
+        <v>43646</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0</v>
+      </c>
+      <c r="D336" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="337" ht="18.75" customHeight="1">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B337" s="22" t="n">
+        <v>43829</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0</v>
+      </c>
+      <c r="D337" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="338" ht="18.75" customHeight="1">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B338" s="22" t="n">
+        <v>44012</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0</v>
+      </c>
+      <c r="D338" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="339" ht="18.75" customHeight="1">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B339" s="22" t="n">
+        <v>44195</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0</v>
+      </c>
+      <c r="D339" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="340" ht="18.75" customHeight="1">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B340" s="22" t="n">
+        <v>44377</v>
+      </c>
+      <c r="C340" t="n">
+        <v>0</v>
+      </c>
+      <c r="D340" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="341" ht="18.75" customHeight="1">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B341" s="22" t="n">
+        <v>44560</v>
+      </c>
+      <c r="C341" t="n">
+        <v>0</v>
+      </c>
+      <c r="D341" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="342" ht="18.75" customHeight="1">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B342" s="22" t="n">
+        <v>44742</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0</v>
+      </c>
+      <c r="D342" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="343" ht="18.75" customHeight="1">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B343" s="22" t="n">
+        <v>44925</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0</v>
+      </c>
+      <c r="D343" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="344" ht="18.75" customHeight="1">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B344" s="22" t="n">
+        <v>45107</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0</v>
+      </c>
+      <c r="D344" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="345" ht="18.75" customHeight="1">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B345" s="22" t="n">
+        <v>45290</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0</v>
+      </c>
+      <c r="D345" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="346" ht="18.75" customHeight="1">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B346" s="22" t="n">
+        <v>45473</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0</v>
+      </c>
+      <c r="D346" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="347" ht="18.75" customHeight="1">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B347" s="22" t="n">
+        <v>45656</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0</v>
+      </c>
+      <c r="D347" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="348" ht="18.75" customHeight="1">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B348" s="22" t="n">
+        <v>45838</v>
+      </c>
+      <c r="C348" t="n">
+        <v>0</v>
+      </c>
+      <c r="D348" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="349" ht="18.75" customHeight="1">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B349" s="22" t="n">
+        <v>46021</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0</v>
+      </c>
+      <c r="D349" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="350" ht="18.75" customHeight="1">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B350" s="22" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0</v>
+      </c>
+      <c r="D350" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="351" ht="18.75" customHeight="1">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B351" s="22" t="n">
+        <v>46386</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0</v>
+      </c>
+      <c r="D351" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="352" ht="18.75" customHeight="1">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B352" s="22" t="n">
+        <v>46568</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0</v>
+      </c>
+      <c r="D352" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="353" ht="18.75" customHeight="1">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B353" s="22" t="n">
+        <v>46751</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0</v>
+      </c>
+      <c r="D353" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="354" ht="18.75" customHeight="1">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B354" s="22" t="n">
+        <v>46934</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0</v>
+      </c>
+      <c r="D354" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="355" ht="18.75" customHeight="1">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B355" s="22" t="n">
+        <v>47117</v>
+      </c>
+      <c r="C355" t="n">
+        <v>0</v>
+      </c>
+      <c r="D355" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="356" ht="18.75" customHeight="1">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B356" s="22" t="n">
+        <v>47299</v>
+      </c>
+      <c r="C356" t="n">
+        <v>0</v>
+      </c>
+      <c r="D356" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="357" ht="18.75" customHeight="1">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B357" s="22" t="n">
+        <v>47482</v>
+      </c>
+      <c r="C357" t="n">
+        <v>0</v>
+      </c>
+      <c r="D357" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="358" ht="18.75" customHeight="1">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B358" s="22" t="n">
+        <v>47664</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0</v>
+      </c>
+      <c r="D358" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="359" ht="18.75" customHeight="1">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B359" s="22" t="n">
+        <v>47847</v>
+      </c>
+      <c r="C359" t="n">
+        <v>0</v>
+      </c>
+      <c r="D359" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="360" ht="18.75" customHeight="1">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B360" s="22" t="n">
+        <v>48029</v>
+      </c>
+      <c r="C360" t="n">
+        <v>0</v>
+      </c>
+      <c r="D360" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="361" ht="18.75" customHeight="1">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B361" s="22" t="n">
+        <v>48212</v>
+      </c>
+      <c r="C361" t="n">
+        <v>0</v>
+      </c>
+      <c r="D361" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="362" ht="18.75" customHeight="1">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B362" s="22" t="n">
+        <v>48395</v>
+      </c>
+      <c r="C362" t="n">
+        <v>0</v>
+      </c>
+      <c r="D362" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="363" ht="18.75" customHeight="1">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B363" s="22" t="n">
+        <v>48578</v>
+      </c>
+      <c r="C363" t="n">
+        <v>0</v>
+      </c>
+      <c r="D363" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="364" ht="18.75" customHeight="1">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B364" s="22" t="n">
+        <v>48760</v>
+      </c>
+      <c r="C364" t="n">
+        <v>0</v>
+      </c>
+      <c r="D364" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="365" ht="18.75" customHeight="1">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B365" s="22" t="n">
+        <v>48943</v>
+      </c>
+      <c r="C365" t="n">
+        <v>0</v>
+      </c>
+      <c r="D365" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="366" ht="18.75" customHeight="1">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B366" s="22" t="n">
+        <v>49125</v>
+      </c>
+      <c r="C366" t="n">
+        <v>0</v>
+      </c>
+      <c r="D366" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="367" ht="18.75" customHeight="1">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B367" s="22" t="n">
+        <v>49308</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0</v>
+      </c>
+      <c r="D367" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="368" ht="18.75" customHeight="1">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B368" s="22" t="n">
+        <v>49490</v>
+      </c>
+      <c r="C368" t="n">
+        <v>0</v>
+      </c>
+      <c r="D368" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="369" ht="18.75" customHeight="1">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B369" s="22" t="n">
+        <v>49673</v>
+      </c>
+      <c r="C369" t="n">
+        <v>0</v>
+      </c>
+      <c r="D369" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="370" ht="18.75" customHeight="1">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B370" s="22" t="n">
+        <v>49856</v>
+      </c>
+      <c r="C370" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D370" t="n">
+        <v>2.298121415</v>
+      </c>
+    </row>
+    <row r="371" ht="18.75" customHeight="1">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B371" s="22" t="n">
+        <v>50039</v>
+      </c>
+      <c r="C371" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D371" t="n">
+        <v>2.183264415</v>
+      </c>
+    </row>
+    <row r="372" ht="18.75" customHeight="1">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B372" s="22" t="n">
+        <v>50221</v>
+      </c>
+      <c r="C372" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D372" t="n">
+        <v>2.068407415</v>
+      </c>
+    </row>
+    <row r="373" ht="18.75" customHeight="1">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B373" s="22" t="n">
+        <v>50404</v>
+      </c>
+      <c r="C373" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D373" t="n">
+        <v>1.953550415</v>
+      </c>
+    </row>
+    <row r="374" ht="18.75" customHeight="1">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B374" s="22" t="n">
+        <v>50586</v>
+      </c>
+      <c r="C374" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D374" t="n">
+        <v>1.838693415</v>
+      </c>
+    </row>
+    <row r="375" ht="18.75" customHeight="1">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B375" s="22" t="n">
+        <v>50769</v>
+      </c>
+      <c r="C375" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D375" t="n">
+        <v>1.723836415</v>
+      </c>
+    </row>
+    <row r="376" ht="18.75" customHeight="1">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B376" s="22" t="n">
+        <v>50951</v>
+      </c>
+      <c r="C376" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D376" t="n">
+        <v>1.608979415</v>
+      </c>
+    </row>
+    <row r="377" ht="18.75" customHeight="1">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B377" s="22" t="n">
+        <v>51134</v>
+      </c>
+      <c r="C377" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D377" t="n">
+        <v>1.494122415</v>
+      </c>
+    </row>
+    <row r="378" ht="18.75" customHeight="1">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B378" s="22" t="n">
+        <v>51317</v>
+      </c>
+      <c r="C378" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D378" t="n">
+        <v>1.379265415</v>
+      </c>
+    </row>
+    <row r="379" ht="18.75" customHeight="1">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B379" s="22" t="n">
+        <v>51500</v>
+      </c>
+      <c r="C379" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D379" t="n">
+        <v>1.264408415</v>
+      </c>
+    </row>
+    <row r="380" ht="18.75" customHeight="1">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B380" s="22" t="n">
+        <v>51682</v>
+      </c>
+      <c r="C380" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D380" t="n">
+        <v>1.149551415</v>
+      </c>
+    </row>
+    <row r="381" ht="18.75" customHeight="1">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B381" s="22" t="n">
+        <v>51865</v>
+      </c>
+      <c r="C381" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D381" t="n">
+        <v>1.034694415</v>
+      </c>
+    </row>
+    <row r="382" ht="18.75" customHeight="1">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B382" s="22" t="n">
+        <v>52047</v>
+      </c>
+      <c r="C382" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D382" t="n">
+        <v>0.9198374150000004</v>
+      </c>
+    </row>
+    <row r="383" ht="18.75" customHeight="1">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B383" s="22" t="n">
+        <v>52230</v>
+      </c>
+      <c r="C383" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D383" t="n">
+        <v>0.8049804150000003</v>
+      </c>
+    </row>
+    <row r="384" ht="18.75" customHeight="1">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B384" s="22" t="n">
+        <v>52412</v>
+      </c>
+      <c r="C384" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D384" t="n">
+        <v>0.6901234150000003</v>
+      </c>
+    </row>
+    <row r="385" ht="18.75" customHeight="1">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B385" s="22" t="n">
+        <v>52595</v>
+      </c>
+      <c r="C385" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D385" t="n">
+        <v>0.5752664150000003</v>
+      </c>
+    </row>
+    <row r="386" ht="18.75" customHeight="1">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B386" s="22" t="n">
+        <v>52778</v>
+      </c>
+      <c r="C386" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D386" t="n">
+        <v>0.4604094150000004</v>
+      </c>
+    </row>
+    <row r="387" ht="18.75" customHeight="1">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B387" s="22" t="n">
+        <v>52961</v>
+      </c>
+      <c r="C387" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0.3455524150000003</v>
+      </c>
+    </row>
+    <row r="388" ht="18.75" customHeight="1">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B388" s="22" t="n">
+        <v>53143</v>
+      </c>
+      <c r="C388" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="D388" t="n">
+        <v>0.2306954150000003</v>
+      </c>
+    </row>
+    <row r="389" ht="18.75" customHeight="1">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>CUAP</t>
+        </is>
+      </c>
+      <c r="B389" s="22" t="n">
+        <v>53326</v>
+      </c>
+      <c r="C389" t="n">
+        <v>7</v>
+      </c>
+      <c r="D389" t="n">
+        <v>0.1158384150000003</v>
+      </c>
+    </row>
+    <row r="390" ht="18.75" customHeight="1">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B390" s="22" t="n">
+        <v>38168</v>
+      </c>
+      <c r="C390" t="n">
+        <v>0</v>
+      </c>
+      <c r="D390" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="391" ht="18.75" customHeight="1">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B391" s="22" t="n">
+        <v>38351</v>
+      </c>
+      <c r="C391" t="n">
+        <v>0</v>
+      </c>
+      <c r="D391" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="392" ht="18.75" customHeight="1">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B392" s="22" t="n">
+        <v>38533</v>
+      </c>
+      <c r="C392" t="n">
+        <v>0</v>
+      </c>
+      <c r="D392" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="393" ht="18.75" customHeight="1">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B393" s="22" t="n">
+        <v>38716</v>
+      </c>
+      <c r="C393" t="n">
+        <v>0</v>
+      </c>
+      <c r="D393" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="394" ht="18.75" customHeight="1">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B394" s="22" t="n">
+        <v>38898</v>
+      </c>
+      <c r="C394" t="n">
+        <v>0</v>
+      </c>
+      <c r="D394" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="395" ht="18.75" customHeight="1">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B395" s="22" t="n">
+        <v>39081</v>
+      </c>
+      <c r="C395" t="n">
+        <v>0</v>
+      </c>
+      <c r="D395" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="396" ht="18.75" customHeight="1">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B396" s="22" t="n">
+        <v>39263</v>
+      </c>
+      <c r="C396" t="n">
+        <v>0</v>
+      </c>
+      <c r="D396" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="397" ht="18.75" customHeight="1">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B397" s="22" t="n">
+        <v>39446</v>
+      </c>
+      <c r="C397" t="n">
+        <v>0</v>
+      </c>
+      <c r="D397" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="398" ht="18.75" customHeight="1">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B398" s="22" t="n">
+        <v>39629</v>
+      </c>
+      <c r="C398" t="n">
+        <v>0</v>
+      </c>
+      <c r="D398" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="399" ht="18.75" customHeight="1">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B399" s="22" t="n">
+        <v>39812</v>
+      </c>
+      <c r="C399" t="n">
+        <v>0</v>
+      </c>
+      <c r="D399" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="400" ht="18.75" customHeight="1">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B400" s="22" t="n">
+        <v>39994</v>
+      </c>
+      <c r="C400" t="n">
+        <v>0</v>
+      </c>
+      <c r="D400" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="401" ht="18.75" customHeight="1">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B401" s="22" t="n">
+        <v>40177</v>
+      </c>
+      <c r="C401" t="n">
+        <v>0</v>
+      </c>
+      <c r="D401" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="402" ht="18.75" customHeight="1">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B402" s="22" t="n">
+        <v>40359</v>
+      </c>
+      <c r="C402" t="n">
+        <v>0</v>
+      </c>
+      <c r="D402" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="403" ht="18.75" customHeight="1">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B403" s="22" t="n">
+        <v>40542</v>
+      </c>
+      <c r="C403" t="n">
+        <v>0</v>
+      </c>
+      <c r="D403" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="404" ht="18.75" customHeight="1">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B404" s="22" t="n">
+        <v>40724</v>
+      </c>
+      <c r="C404" t="n">
+        <v>0</v>
+      </c>
+      <c r="D404" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="405" ht="18.75" customHeight="1">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B405" s="22" t="n">
+        <v>40907</v>
+      </c>
+      <c r="C405" t="n">
+        <v>0</v>
+      </c>
+      <c r="D405" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="406" ht="18.75" customHeight="1">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B406" s="22" t="n">
+        <v>41090</v>
+      </c>
+      <c r="C406" t="n">
+        <v>0</v>
+      </c>
+      <c r="D406" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="407" ht="18.75" customHeight="1">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B407" s="22" t="n">
+        <v>41273</v>
+      </c>
+      <c r="C407" t="n">
+        <v>0</v>
+      </c>
+      <c r="D407" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="408" ht="18.75" customHeight="1">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B408" s="22" t="n">
+        <v>41455</v>
+      </c>
+      <c r="C408" t="n">
+        <v>0</v>
+      </c>
+      <c r="D408" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="409" ht="18.75" customHeight="1">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B409" s="22" t="n">
+        <v>41638</v>
+      </c>
+      <c r="C409" t="n">
+        <v>0</v>
+      </c>
+      <c r="D409" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="410" ht="18.75" customHeight="1">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B410" s="22" t="n">
+        <v>41820</v>
+      </c>
+      <c r="C410" t="n">
+        <v>0</v>
+      </c>
+      <c r="D410" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="411" ht="18.75" customHeight="1">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B411" s="22" t="n">
+        <v>42003</v>
+      </c>
+      <c r="C411" t="n">
+        <v>0</v>
+      </c>
+      <c r="D411" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="412" ht="18.75" customHeight="1">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B412" s="22" t="n">
+        <v>42185</v>
+      </c>
+      <c r="C412" t="n">
+        <v>0</v>
+      </c>
+      <c r="D412" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="413" ht="18.75" customHeight="1">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B413" s="22" t="n">
+        <v>42368</v>
+      </c>
+      <c r="C413" t="n">
+        <v>0</v>
+      </c>
+      <c r="D413" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="414" ht="18.75" customHeight="1">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B414" s="22" t="n">
+        <v>42551</v>
+      </c>
+      <c r="C414" t="n">
+        <v>0</v>
+      </c>
+      <c r="D414" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="415" ht="18.75" customHeight="1">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B415" s="22" t="n">
+        <v>42734</v>
+      </c>
+      <c r="C415" t="n">
+        <v>0</v>
+      </c>
+      <c r="D415" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="416" ht="18.75" customHeight="1">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B416" s="22" t="n">
+        <v>42916</v>
+      </c>
+      <c r="C416" t="n">
+        <v>0</v>
+      </c>
+      <c r="D416" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="417" ht="18.75" customHeight="1">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B417" s="22" t="n">
+        <v>43099</v>
+      </c>
+      <c r="C417" t="n">
+        <v>0</v>
+      </c>
+      <c r="D417" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="418" ht="18.75" customHeight="1">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B418" s="22" t="n">
+        <v>43281</v>
+      </c>
+      <c r="C418" t="n">
+        <v>0</v>
+      </c>
+      <c r="D418" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="419" ht="18.75" customHeight="1">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B419" s="22" t="n">
+        <v>43464</v>
+      </c>
+      <c r="C419" t="n">
+        <v>0</v>
+      </c>
+      <c r="D419" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="420" ht="18.75" customHeight="1">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B420" s="22" t="n">
+        <v>43646</v>
+      </c>
+      <c r="C420" t="n">
+        <v>0</v>
+      </c>
+      <c r="D420" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="421" ht="18.75" customHeight="1">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B421" s="22" t="n">
+        <v>43829</v>
+      </c>
+      <c r="C421" t="n">
+        <v>0</v>
+      </c>
+      <c r="D421" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="422" ht="18.75" customHeight="1">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B422" s="22" t="n">
+        <v>44012</v>
+      </c>
+      <c r="C422" t="n">
+        <v>0</v>
+      </c>
+      <c r="D422" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="423" ht="18.75" customHeight="1">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B423" s="22" t="n">
+        <v>44195</v>
+      </c>
+      <c r="C423" t="n">
+        <v>0</v>
+      </c>
+      <c r="D423" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="424" ht="18.75" customHeight="1">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B424" s="22" t="n">
+        <v>44377</v>
+      </c>
+      <c r="C424" t="n">
+        <v>0</v>
+      </c>
+      <c r="D424" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="425" ht="18.75" customHeight="1">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B425" s="22" t="n">
+        <v>44560</v>
+      </c>
+      <c r="C425" t="n">
+        <v>0</v>
+      </c>
+      <c r="D425" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="426" ht="18.75" customHeight="1">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B426" s="22" t="n">
+        <v>44742</v>
+      </c>
+      <c r="C426" t="n">
+        <v>0</v>
+      </c>
+      <c r="D426" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="427" ht="18.75" customHeight="1">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B427" s="22" t="n">
+        <v>44925</v>
+      </c>
+      <c r="C427" t="n">
+        <v>0</v>
+      </c>
+      <c r="D427" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="428" ht="18.75" customHeight="1">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B428" s="22" t="n">
+        <v>45107</v>
+      </c>
+      <c r="C428" t="n">
+        <v>0</v>
+      </c>
+      <c r="D428" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="429" ht="18.75" customHeight="1">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B429" s="22" t="n">
+        <v>45290</v>
+      </c>
+      <c r="C429" t="n">
+        <v>0</v>
+      </c>
+      <c r="D429" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="430" ht="18.75" customHeight="1">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B430" s="22" t="n">
+        <v>45473</v>
+      </c>
+      <c r="C430" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D430" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="431" ht="18.75" customHeight="1">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B431" s="22" t="n">
+        <v>45656</v>
+      </c>
+      <c r="C431" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D431" t="n">
+        <v>3.516763855000001</v>
+      </c>
+    </row>
+    <row r="432" ht="18.75" customHeight="1">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B432" s="22" t="n">
+        <v>45838</v>
+      </c>
+      <c r="C432" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D432" t="n">
+        <v>3.331661355</v>
+      </c>
+    </row>
+    <row r="433" ht="18.75" customHeight="1">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B433" s="22" t="n">
+        <v>46021</v>
+      </c>
+      <c r="C433" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D433" t="n">
+        <v>3.146558855</v>
+      </c>
+    </row>
+    <row r="434" ht="18.75" customHeight="1">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B434" s="22" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C434" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D434" t="n">
+        <v>2.961456355000001</v>
+      </c>
+    </row>
+    <row r="435" ht="18.75" customHeight="1">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B435" s="22" t="n">
+        <v>46386</v>
+      </c>
+      <c r="C435" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D435" t="n">
+        <v>2.776353855000001</v>
+      </c>
+    </row>
+    <row r="436" ht="18.75" customHeight="1">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B436" s="22" t="n">
+        <v>46568</v>
+      </c>
+      <c r="C436" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D436" t="n">
+        <v>2.591251355000001</v>
+      </c>
+    </row>
+    <row r="437" ht="18.75" customHeight="1">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B437" s="22" t="n">
+        <v>46751</v>
+      </c>
+      <c r="C437" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D437" t="n">
+        <v>2.406148855000001</v>
+      </c>
+    </row>
+    <row r="438" ht="18.75" customHeight="1">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B438" s="22" t="n">
+        <v>46934</v>
+      </c>
+      <c r="C438" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D438" t="n">
+        <v>2.221046355000001</v>
+      </c>
+    </row>
+    <row r="439" ht="18.75" customHeight="1">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B439" s="22" t="n">
+        <v>47117</v>
+      </c>
+      <c r="C439" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D439" t="n">
+        <v>2.035943855000002</v>
+      </c>
+    </row>
+    <row r="440" ht="18.75" customHeight="1">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B440" s="22" t="n">
+        <v>47299</v>
+      </c>
+      <c r="C440" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D440" t="n">
+        <v>1.850841355000002</v>
+      </c>
+    </row>
+    <row r="441" ht="18.75" customHeight="1">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B441" s="22" t="n">
+        <v>47482</v>
+      </c>
+      <c r="C441" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D441" t="n">
+        <v>1.665738855000001</v>
+      </c>
+    </row>
+    <row r="442" ht="18.75" customHeight="1">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B442" s="22" t="n">
+        <v>47664</v>
+      </c>
+      <c r="C442" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D442" t="n">
+        <v>1.480636355000001</v>
+      </c>
+    </row>
+    <row r="443" ht="18.75" customHeight="1">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B443" s="22" t="n">
+        <v>47847</v>
+      </c>
+      <c r="C443" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D443" t="n">
+        <v>1.295533855000001</v>
+      </c>
+    </row>
+    <row r="444" ht="18.75" customHeight="1">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B444" s="22" t="n">
+        <v>48029</v>
+      </c>
+      <c r="C444" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D444" t="n">
+        <v>1.110431355000001</v>
+      </c>
+    </row>
+    <row r="445" ht="18.75" customHeight="1">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B445" s="22" t="n">
+        <v>48212</v>
+      </c>
+      <c r="C445" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D445" t="n">
+        <v>0.9253288550000013</v>
+      </c>
+    </row>
+    <row r="446" ht="18.75" customHeight="1">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B446" s="22" t="n">
+        <v>48395</v>
+      </c>
+      <c r="C446" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D446" t="n">
+        <v>0.7402263550000013</v>
+      </c>
+    </row>
+    <row r="447" ht="18.75" customHeight="1">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B447" s="22" t="n">
+        <v>48578</v>
+      </c>
+      <c r="C447" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D447" t="n">
+        <v>0.5551238550000013</v>
+      </c>
+    </row>
+    <row r="448" ht="18.75" customHeight="1">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B448" s="22" t="n">
+        <v>48760</v>
+      </c>
+      <c r="C448" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D448" t="n">
+        <v>0.3700213550000013</v>
+      </c>
+    </row>
+    <row r="449" ht="18.75" customHeight="1">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>DICP</t>
+        </is>
+      </c>
+      <c r="B449" s="22" t="n">
+        <v>48944</v>
+      </c>
+      <c r="C449" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="D449" t="n">
+        <v>0.1849188550000013</v>
+      </c>
+    </row>
+    <row r="450" ht="18.75" customHeight="1">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B450" s="22" t="n">
+        <v>38168</v>
+      </c>
+      <c r="C450" t="n">
+        <v>0</v>
+      </c>
+      <c r="D450" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="451" ht="18.75" customHeight="1">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B451" s="22" t="n">
+        <v>38351</v>
+      </c>
+      <c r="C451" t="n">
+        <v>0</v>
+      </c>
+      <c r="D451" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="452" ht="18.75" customHeight="1">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B452" s="22" t="n">
+        <v>38533</v>
+      </c>
+      <c r="C452" t="n">
+        <v>0</v>
+      </c>
+      <c r="D452" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="453" ht="18.75" customHeight="1">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B453" s="22" t="n">
+        <v>38716</v>
+      </c>
+      <c r="C453" t="n">
+        <v>0</v>
+      </c>
+      <c r="D453" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="454" ht="18.75" customHeight="1">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B454" s="22" t="n">
+        <v>38898</v>
+      </c>
+      <c r="C454" t="n">
+        <v>0</v>
+      </c>
+      <c r="D454" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="455" ht="18.75" customHeight="1">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B455" s="22" t="n">
+        <v>39081</v>
+      </c>
+      <c r="C455" t="n">
+        <v>0</v>
+      </c>
+      <c r="D455" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="456" ht="18.75" customHeight="1">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B456" s="22" t="n">
+        <v>39263</v>
+      </c>
+      <c r="C456" t="n">
+        <v>0</v>
+      </c>
+      <c r="D456" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="457" ht="18.75" customHeight="1">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B457" s="22" t="n">
+        <v>39446</v>
+      </c>
+      <c r="C457" t="n">
+        <v>0</v>
+      </c>
+      <c r="D457" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="458" ht="18.75" customHeight="1">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B458" s="22" t="n">
+        <v>39629</v>
+      </c>
+      <c r="C458" t="n">
+        <v>0</v>
+      </c>
+      <c r="D458" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="459" ht="18.75" customHeight="1">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B459" s="22" t="n">
+        <v>39812</v>
+      </c>
+      <c r="C459" t="n">
+        <v>0</v>
+      </c>
+      <c r="D459" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="460" ht="18.75" customHeight="1">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B460" s="22" t="n">
+        <v>39994</v>
+      </c>
+      <c r="C460" t="n">
+        <v>0</v>
+      </c>
+      <c r="D460" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="461" ht="18.75" customHeight="1">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B461" s="22" t="n">
+        <v>40177</v>
+      </c>
+      <c r="C461" t="n">
+        <v>0</v>
+      </c>
+      <c r="D461" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="462" ht="18.75" customHeight="1">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B462" s="22" t="n">
+        <v>40359</v>
+      </c>
+      <c r="C462" t="n">
+        <v>0</v>
+      </c>
+      <c r="D462" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="463" ht="18.75" customHeight="1">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B463" s="22" t="n">
+        <v>40542</v>
+      </c>
+      <c r="C463" t="n">
+        <v>0</v>
+      </c>
+      <c r="D463" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="464" ht="18.75" customHeight="1">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B464" s="22" t="n">
+        <v>40724</v>
+      </c>
+      <c r="C464" t="n">
+        <v>0</v>
+      </c>
+      <c r="D464" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="465" ht="18.75" customHeight="1">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B465" s="22" t="n">
+        <v>40907</v>
+      </c>
+      <c r="C465" t="n">
+        <v>0</v>
+      </c>
+      <c r="D465" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="466" ht="18.75" customHeight="1">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B466" s="22" t="n">
+        <v>41090</v>
+      </c>
+      <c r="C466" t="n">
+        <v>0</v>
+      </c>
+      <c r="D466" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="467" ht="18.75" customHeight="1">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B467" s="22" t="n">
+        <v>41273</v>
+      </c>
+      <c r="C467" t="n">
+        <v>0</v>
+      </c>
+      <c r="D467" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="468" ht="18.75" customHeight="1">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B468" s="22" t="n">
+        <v>41455</v>
+      </c>
+      <c r="C468" t="n">
+        <v>0</v>
+      </c>
+      <c r="D468" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="469" ht="18.75" customHeight="1">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B469" s="22" t="n">
+        <v>41638</v>
+      </c>
+      <c r="C469" t="n">
+        <v>0</v>
+      </c>
+      <c r="D469" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="470" ht="18.75" customHeight="1">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B470" s="22" t="n">
+        <v>41820</v>
+      </c>
+      <c r="C470" t="n">
+        <v>0</v>
+      </c>
+      <c r="D470" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="471" ht="18.75" customHeight="1">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B471" s="22" t="n">
+        <v>42003</v>
+      </c>
+      <c r="C471" t="n">
+        <v>0</v>
+      </c>
+      <c r="D471" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="472" ht="18.75" customHeight="1">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B472" s="22" t="n">
+        <v>42185</v>
+      </c>
+      <c r="C472" t="n">
+        <v>0</v>
+      </c>
+      <c r="D472" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="473" ht="18.75" customHeight="1">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B473" s="22" t="n">
+        <v>42368</v>
+      </c>
+      <c r="C473" t="n">
+        <v>0</v>
+      </c>
+      <c r="D473" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="474" ht="18.75" customHeight="1">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B474" s="22" t="n">
+        <v>42551</v>
+      </c>
+      <c r="C474" t="n">
+        <v>0</v>
+      </c>
+      <c r="D474" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="475" ht="18.75" customHeight="1">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B475" s="22" t="n">
+        <v>42734</v>
+      </c>
+      <c r="C475" t="n">
+        <v>0</v>
+      </c>
+      <c r="D475" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="476" ht="18.75" customHeight="1">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B476" s="22" t="n">
+        <v>42916</v>
+      </c>
+      <c r="C476" t="n">
+        <v>0</v>
+      </c>
+      <c r="D476" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="477" ht="18.75" customHeight="1">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B477" s="22" t="n">
+        <v>43099</v>
+      </c>
+      <c r="C477" t="n">
+        <v>0</v>
+      </c>
+      <c r="D477" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="478" ht="18.75" customHeight="1">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B478" s="22" t="n">
+        <v>43281</v>
+      </c>
+      <c r="C478" t="n">
+        <v>0</v>
+      </c>
+      <c r="D478" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="479" ht="18.75" customHeight="1">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B479" s="22" t="n">
+        <v>43464</v>
+      </c>
+      <c r="C479" t="n">
+        <v>0</v>
+      </c>
+      <c r="D479" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="480" ht="18.75" customHeight="1">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B480" s="22" t="n">
+        <v>43646</v>
+      </c>
+      <c r="C480" t="n">
+        <v>0</v>
+      </c>
+      <c r="D480" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="481" ht="18.75" customHeight="1">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B481" s="22" t="n">
+        <v>43829</v>
+      </c>
+      <c r="C481" t="n">
+        <v>0</v>
+      </c>
+      <c r="D481" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="482" ht="18.75" customHeight="1">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B482" s="22" t="n">
+        <v>44012</v>
+      </c>
+      <c r="C482" t="n">
+        <v>0</v>
+      </c>
+      <c r="D482" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="483" ht="18.75" customHeight="1">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B483" s="22" t="n">
+        <v>44195</v>
+      </c>
+      <c r="C483" t="n">
+        <v>0</v>
+      </c>
+      <c r="D483" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="484" ht="18.75" customHeight="1">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B484" s="22" t="n">
+        <v>44377</v>
+      </c>
+      <c r="C484" t="n">
+        <v>0</v>
+      </c>
+      <c r="D484" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="485" ht="18.75" customHeight="1">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B485" s="22" t="n">
+        <v>44560</v>
+      </c>
+      <c r="C485" t="n">
+        <v>0</v>
+      </c>
+      <c r="D485" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="486" ht="18.75" customHeight="1">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B486" s="22" t="n">
+        <v>44742</v>
+      </c>
+      <c r="C486" t="n">
+        <v>0</v>
+      </c>
+      <c r="D486" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="487" ht="18.75" customHeight="1">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B487" s="22" t="n">
+        <v>44925</v>
+      </c>
+      <c r="C487" t="n">
+        <v>0</v>
+      </c>
+      <c r="D487" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="488" ht="18.75" customHeight="1">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B488" s="22" t="n">
+        <v>45107</v>
+      </c>
+      <c r="C488" t="n">
+        <v>0</v>
+      </c>
+      <c r="D488" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="489" ht="18.75" customHeight="1">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B489" s="22" t="n">
+        <v>45290</v>
+      </c>
+      <c r="C489" t="n">
+        <v>0</v>
+      </c>
+      <c r="D489" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="490" ht="18.75" customHeight="1">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B490" s="22" t="n">
+        <v>45473</v>
+      </c>
+      <c r="C490" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D490" t="n">
+        <v>3.701866355</v>
+      </c>
+    </row>
+    <row r="491" ht="18.75" customHeight="1">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B491" s="22" t="n">
+        <v>45656</v>
+      </c>
+      <c r="C491" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D491" t="n">
+        <v>3.516763855000001</v>
+      </c>
+    </row>
+    <row r="492" ht="18.75" customHeight="1">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B492" s="22" t="n">
+        <v>45838</v>
+      </c>
+      <c r="C492" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D492" t="n">
+        <v>3.331661355</v>
+      </c>
+    </row>
+    <row r="493" ht="18.75" customHeight="1">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B493" s="22" t="n">
+        <v>46021</v>
+      </c>
+      <c r="C493" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D493" t="n">
+        <v>3.146558855</v>
+      </c>
+    </row>
+    <row r="494" ht="18.75" customHeight="1">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B494" s="22" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C494" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D494" t="n">
+        <v>2.961456355000001</v>
+      </c>
+    </row>
+    <row r="495" ht="18.75" customHeight="1">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B495" s="22" t="n">
+        <v>46386</v>
+      </c>
+      <c r="C495" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D495" t="n">
+        <v>2.776353855000001</v>
+      </c>
+    </row>
+    <row r="496" ht="18.75" customHeight="1">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B496" s="22" t="n">
+        <v>46568</v>
+      </c>
+      <c r="C496" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D496" t="n">
+        <v>2.591251355000001</v>
+      </c>
+    </row>
+    <row r="497" ht="18.75" customHeight="1">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B497" s="22" t="n">
+        <v>46751</v>
+      </c>
+      <c r="C497" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D497" t="n">
+        <v>2.406148855000001</v>
+      </c>
+    </row>
+    <row r="498" ht="18.75" customHeight="1">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B498" s="22" t="n">
+        <v>46934</v>
+      </c>
+      <c r="C498" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D498" t="n">
+        <v>2.221046355000001</v>
+      </c>
+    </row>
+    <row r="499" ht="18.75" customHeight="1">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B499" s="22" t="n">
+        <v>47117</v>
+      </c>
+      <c r="C499" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D499" t="n">
+        <v>2.035943855000002</v>
+      </c>
+    </row>
+    <row r="500" ht="18.75" customHeight="1">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B500" s="22" t="n">
+        <v>47299</v>
+      </c>
+      <c r="C500" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D500" t="n">
+        <v>1.850841355000002</v>
+      </c>
+    </row>
+    <row r="501" ht="18.75" customHeight="1">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B501" s="22" t="n">
+        <v>47482</v>
+      </c>
+      <c r="C501" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D501" t="n">
+        <v>1.665738855000001</v>
+      </c>
+    </row>
+    <row r="502" ht="18.75" customHeight="1">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B502" s="22" t="n">
+        <v>47664</v>
+      </c>
+      <c r="C502" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D502" t="n">
+        <v>1.480636355000001</v>
+      </c>
+    </row>
+    <row r="503" ht="18.75" customHeight="1">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B503" s="22" t="n">
+        <v>47847</v>
+      </c>
+      <c r="C503" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D503" t="n">
+        <v>1.295533855000001</v>
+      </c>
+    </row>
+    <row r="504" ht="18.75" customHeight="1">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B504" s="22" t="n">
+        <v>48029</v>
+      </c>
+      <c r="C504" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D504" t="n">
+        <v>1.110431355000001</v>
+      </c>
+    </row>
+    <row r="505" ht="18.75" customHeight="1">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B505" s="22" t="n">
+        <v>48212</v>
+      </c>
+      <c r="C505" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D505" t="n">
+        <v>0.9253288550000013</v>
+      </c>
+    </row>
+    <row r="506" ht="18.75" customHeight="1">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B506" s="22" t="n">
+        <v>48395</v>
+      </c>
+      <c r="C506" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D506" t="n">
+        <v>0.7402263550000013</v>
+      </c>
+    </row>
+    <row r="507" ht="18.75" customHeight="1">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B507" s="22" t="n">
+        <v>48578</v>
+      </c>
+      <c r="C507" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D507" t="n">
+        <v>0.5551238550000013</v>
+      </c>
+    </row>
+    <row r="508" ht="18.75" customHeight="1">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B508" s="22" t="n">
+        <v>48760</v>
+      </c>
+      <c r="C508" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D508" t="n">
+        <v>0.3700213550000013</v>
+      </c>
+    </row>
+    <row r="509" ht="18.75" customHeight="1">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>DIP0</t>
+        </is>
+      </c>
+      <c r="B509" s="22" t="n">
+        <v>48944</v>
+      </c>
+      <c r="C509" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="D509" t="n">
+        <v>0.1849188550000013</v>
+      </c>
+    </row>
     <row r="510" ht="18.75" customHeight="1"/>
     <row r="511" ht="18.75" customHeight="1"/>
     <row r="512" ht="18.75" customHeight="1"/>

--- a/data/instruments_master.xlsx
+++ b/data/instruments_master.xlsx
@@ -3917,7 +3917,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D509"/>
+  <dimension ref="A1:D714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.57642857142857" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -12668,34 +12668,3286 @@
         <v>0.1849188550000013</v>
       </c>
     </row>
-    <row r="510" ht="18.75" customHeight="1"/>
-    <row r="511" ht="18.75" customHeight="1"/>
-    <row r="512" ht="18.75" customHeight="1"/>
-    <row r="513" ht="18.75" customHeight="1"/>
-    <row r="514" ht="18.75" customHeight="1"/>
-    <row r="515" ht="18.75" customHeight="1"/>
-    <row r="516" ht="18.75" customHeight="1"/>
-    <row r="517" ht="18.75" customHeight="1"/>
-    <row r="518" ht="18.75" customHeight="1"/>
-    <row r="519" ht="18.75" customHeight="1"/>
-    <row r="520" ht="18.75" customHeight="1"/>
-    <row r="521" ht="18.75" customHeight="1"/>
-    <row r="522" ht="18.75" customHeight="1"/>
-    <row r="523" ht="18.75" customHeight="1"/>
-    <row r="524" ht="18.75" customHeight="1"/>
-    <row r="525" ht="18.75" customHeight="1"/>
-    <row r="526" ht="18.75" customHeight="1"/>
-    <row r="527" ht="18.75" customHeight="1"/>
-    <row r="528" ht="18.75" customHeight="1"/>
-    <row r="529" ht="18.75" customHeight="1"/>
-    <row r="530" ht="18.75" customHeight="1"/>
-    <row r="531" ht="18.75" customHeight="1"/>
-    <row r="532" ht="18.75" customHeight="1"/>
-    <row r="533" ht="18.75" customHeight="1"/>
-    <row r="534" ht="18.75" customHeight="1"/>
-    <row r="535" ht="18.75" customHeight="1"/>
-    <row r="536" ht="18.75" customHeight="1"/>
-    <row r="537" ht="18.75" customHeight="1"/>
+    <row r="510" ht="18.75" customHeight="1">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>TX26</t>
+        </is>
+      </c>
+      <c r="B510" s="22" t="n">
+        <v>44144</v>
+      </c>
+      <c r="C510" t="n">
+        <v>0</v>
+      </c>
+      <c r="D510" t="n">
+        <v>0.361111111</v>
+      </c>
+    </row>
+    <row r="511" ht="18.75" customHeight="1">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>TX26</t>
+        </is>
+      </c>
+      <c r="B511" s="22" t="n">
+        <v>44325</v>
+      </c>
+      <c r="C511" t="n">
+        <v>0</v>
+      </c>
+      <c r="D511" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="512" ht="18.75" customHeight="1">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>TX26</t>
+        </is>
+      </c>
+      <c r="B512" s="22" t="n">
+        <v>44509</v>
+      </c>
+      <c r="C512" t="n">
+        <v>0</v>
+      </c>
+      <c r="D512" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="513" ht="18.75" customHeight="1">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>TX26</t>
+        </is>
+      </c>
+      <c r="B513" s="22" t="n">
+        <v>44690</v>
+      </c>
+      <c r="C513" t="n">
+        <v>0</v>
+      </c>
+      <c r="D513" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="514" ht="18.75" customHeight="1">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>TX26</t>
+        </is>
+      </c>
+      <c r="B514" s="22" t="n">
+        <v>44874</v>
+      </c>
+      <c r="C514" t="n">
+        <v>0</v>
+      </c>
+      <c r="D514" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="515" ht="18.75" customHeight="1">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>TX26</t>
+        </is>
+      </c>
+      <c r="B515" s="22" t="n">
+        <v>45055</v>
+      </c>
+      <c r="C515" t="n">
+        <v>0</v>
+      </c>
+      <c r="D515" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="516" ht="18.75" customHeight="1">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>TX26</t>
+        </is>
+      </c>
+      <c r="B516" s="22" t="n">
+        <v>45239</v>
+      </c>
+      <c r="C516" t="n">
+        <v>0</v>
+      </c>
+      <c r="D516" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517" ht="18.75" customHeight="1">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>TX26</t>
+        </is>
+      </c>
+      <c r="B517" s="22" t="n">
+        <v>45421</v>
+      </c>
+      <c r="C517" t="n">
+        <v>0</v>
+      </c>
+      <c r="D517" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518" ht="18.75" customHeight="1">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>TX26</t>
+        </is>
+      </c>
+      <c r="B518" s="22" t="n">
+        <v>45605</v>
+      </c>
+      <c r="C518" t="n">
+        <v>20</v>
+      </c>
+      <c r="D518" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="519" ht="18.75" customHeight="1">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>TX26</t>
+        </is>
+      </c>
+      <c r="B519" s="22" t="n">
+        <v>45786</v>
+      </c>
+      <c r="C519" t="n">
+        <v>20</v>
+      </c>
+      <c r="D519" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="520" ht="18.75" customHeight="1">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>TX26</t>
+        </is>
+      </c>
+      <c r="B520" s="22" t="n">
+        <v>45970</v>
+      </c>
+      <c r="C520" t="n">
+        <v>20</v>
+      </c>
+      <c r="D520" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="521" ht="18.75" customHeight="1">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>TX26</t>
+        </is>
+      </c>
+      <c r="B521" s="22" t="n">
+        <v>46151</v>
+      </c>
+      <c r="C521" t="n">
+        <v>20</v>
+      </c>
+      <c r="D521" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="522" ht="18.75" customHeight="1">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>TX26</t>
+        </is>
+      </c>
+      <c r="B522" s="22" t="n">
+        <v>46335</v>
+      </c>
+      <c r="C522" t="n">
+        <v>20</v>
+      </c>
+      <c r="D522" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="523" ht="18.75" customHeight="1">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B523" s="22" t="n">
+        <v>44144</v>
+      </c>
+      <c r="C523" t="n">
+        <v>0</v>
+      </c>
+      <c r="D523" t="n">
+        <v>0.40625</v>
+      </c>
+    </row>
+    <row r="524" ht="18.75" customHeight="1">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B524" s="22" t="n">
+        <v>44325</v>
+      </c>
+      <c r="C524" t="n">
+        <v>0</v>
+      </c>
+      <c r="D524" t="n">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="525" ht="18.75" customHeight="1">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B525" s="22" t="n">
+        <v>44509</v>
+      </c>
+      <c r="C525" t="n">
+        <v>0</v>
+      </c>
+      <c r="D525" t="n">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="526" ht="18.75" customHeight="1">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B526" s="22" t="n">
+        <v>44690</v>
+      </c>
+      <c r="C526" t="n">
+        <v>0</v>
+      </c>
+      <c r="D526" t="n">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="527" ht="18.75" customHeight="1">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B527" s="22" t="n">
+        <v>44874</v>
+      </c>
+      <c r="C527" t="n">
+        <v>0</v>
+      </c>
+      <c r="D527" t="n">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="528" ht="18.75" customHeight="1">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B528" s="22" t="n">
+        <v>45055</v>
+      </c>
+      <c r="C528" t="n">
+        <v>0</v>
+      </c>
+      <c r="D528" t="n">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="529" ht="18.75" customHeight="1">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B529" s="22" t="n">
+        <v>45239</v>
+      </c>
+      <c r="C529" t="n">
+        <v>0</v>
+      </c>
+      <c r="D529" t="n">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="530" ht="18.75" customHeight="1">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B530" s="22" t="n">
+        <v>45421</v>
+      </c>
+      <c r="C530" t="n">
+        <v>10</v>
+      </c>
+      <c r="D530" t="n">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="531" ht="18.75" customHeight="1">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B531" s="22" t="n">
+        <v>45605</v>
+      </c>
+      <c r="C531" t="n">
+        <v>10</v>
+      </c>
+      <c r="D531" t="n">
+        <v>1.0125</v>
+      </c>
+    </row>
+    <row r="532" ht="18.75" customHeight="1">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B532" s="22" t="n">
+        <v>45786</v>
+      </c>
+      <c r="C532" t="n">
+        <v>10</v>
+      </c>
+      <c r="D532" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="533" ht="18.75" customHeight="1">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B533" s="22" t="n">
+        <v>45970</v>
+      </c>
+      <c r="C533" t="n">
+        <v>10</v>
+      </c>
+      <c r="D533" t="n">
+        <v>0.7875</v>
+      </c>
+    </row>
+    <row r="534" ht="18.75" customHeight="1">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B534" s="22" t="n">
+        <v>46151</v>
+      </c>
+      <c r="C534" t="n">
+        <v>10</v>
+      </c>
+      <c r="D534" t="n">
+        <v>0.675</v>
+      </c>
+    </row>
+    <row r="535" ht="18.75" customHeight="1">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B535" s="22" t="n">
+        <v>46335</v>
+      </c>
+      <c r="C535" t="n">
+        <v>10</v>
+      </c>
+      <c r="D535" t="n">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="536" ht="18.75" customHeight="1">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B536" s="22" t="n">
+        <v>46516</v>
+      </c>
+      <c r="C536" t="n">
+        <v>10</v>
+      </c>
+      <c r="D536" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="537" ht="18.75" customHeight="1">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B537" s="22" t="n">
+        <v>46700</v>
+      </c>
+      <c r="C537" t="n">
+        <v>10</v>
+      </c>
+      <c r="D537" t="n">
+        <v>0.3375</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B538" s="22" t="n">
+        <v>46882</v>
+      </c>
+      <c r="C538" t="n">
+        <v>10</v>
+      </c>
+      <c r="D538" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>TX28</t>
+        </is>
+      </c>
+      <c r="B539" s="22" t="n">
+        <v>47066</v>
+      </c>
+      <c r="C539" t="n">
+        <v>10</v>
+      </c>
+      <c r="D539" t="n">
+        <v>0.1125</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B540" s="22" t="n">
+        <v>44895</v>
+      </c>
+      <c r="C540" t="n">
+        <v>0</v>
+      </c>
+      <c r="D540" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B541" s="22" t="n">
+        <v>45076</v>
+      </c>
+      <c r="C541" t="n">
+        <v>0</v>
+      </c>
+      <c r="D541" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B542" s="22" t="n">
+        <v>45260</v>
+      </c>
+      <c r="C542" t="n">
+        <v>0</v>
+      </c>
+      <c r="D542" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B543" s="22" t="n">
+        <v>45442</v>
+      </c>
+      <c r="C543" t="n">
+        <v>0</v>
+      </c>
+      <c r="D543" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B544" s="22" t="n">
+        <v>45626</v>
+      </c>
+      <c r="C544" t="n">
+        <v>0</v>
+      </c>
+      <c r="D544" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B545" s="22" t="n">
+        <v>45807</v>
+      </c>
+      <c r="C545" t="n">
+        <v>0</v>
+      </c>
+      <c r="D545" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B546" s="22" t="n">
+        <v>45991</v>
+      </c>
+      <c r="C546" t="n">
+        <v>0</v>
+      </c>
+      <c r="D546" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B547" s="22" t="n">
+        <v>46172</v>
+      </c>
+      <c r="C547" t="n">
+        <v>0</v>
+      </c>
+      <c r="D547" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B548" s="22" t="n">
+        <v>46356</v>
+      </c>
+      <c r="C548" t="n">
+        <v>0</v>
+      </c>
+      <c r="D548" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B549" s="22" t="n">
+        <v>46537</v>
+      </c>
+      <c r="C549" t="n">
+        <v>10</v>
+      </c>
+      <c r="D549" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B550" s="22" t="n">
+        <v>46721</v>
+      </c>
+      <c r="C550" t="n">
+        <v>10</v>
+      </c>
+      <c r="D550" t="n">
+        <v>1.125</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B551" s="22" t="n">
+        <v>46903</v>
+      </c>
+      <c r="C551" t="n">
+        <v>10</v>
+      </c>
+      <c r="D551" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B552" s="22" t="n">
+        <v>47087</v>
+      </c>
+      <c r="C552" t="n">
+        <v>10</v>
+      </c>
+      <c r="D552" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B553" s="22" t="n">
+        <v>47268</v>
+      </c>
+      <c r="C553" t="n">
+        <v>10</v>
+      </c>
+      <c r="D553" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B554" s="22" t="n">
+        <v>47452</v>
+      </c>
+      <c r="C554" t="n">
+        <v>10</v>
+      </c>
+      <c r="D554" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B555" s="22" t="n">
+        <v>47633</v>
+      </c>
+      <c r="C555" t="n">
+        <v>10</v>
+      </c>
+      <c r="D555" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B556" s="22" t="n">
+        <v>47817</v>
+      </c>
+      <c r="C556" t="n">
+        <v>10</v>
+      </c>
+      <c r="D556" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B557" s="22" t="n">
+        <v>47998</v>
+      </c>
+      <c r="C557" t="n">
+        <v>10</v>
+      </c>
+      <c r="D557" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>TX31</t>
+        </is>
+      </c>
+      <c r="B558" s="22" t="n">
+        <v>48182</v>
+      </c>
+      <c r="C558" t="n">
+        <v>10</v>
+      </c>
+      <c r="D558" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B559" s="22" t="n">
+        <v>38076</v>
+      </c>
+      <c r="C559" t="n">
+        <v>0</v>
+      </c>
+      <c r="D559" t="n">
+        <v>0.4425</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B560" s="22" t="n">
+        <v>38260</v>
+      </c>
+      <c r="C560" t="n">
+        <v>0</v>
+      </c>
+      <c r="D560" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B561" s="22" t="n">
+        <v>38441</v>
+      </c>
+      <c r="C561" t="n">
+        <v>0</v>
+      </c>
+      <c r="D561" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B562" s="22" t="n">
+        <v>38625</v>
+      </c>
+      <c r="C562" t="n">
+        <v>0</v>
+      </c>
+      <c r="D562" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B563" s="22" t="n">
+        <v>38806</v>
+      </c>
+      <c r="C563" t="n">
+        <v>0</v>
+      </c>
+      <c r="D563" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B564" s="22" t="n">
+        <v>38990</v>
+      </c>
+      <c r="C564" t="n">
+        <v>0</v>
+      </c>
+      <c r="D564" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B565" s="22" t="n">
+        <v>39171</v>
+      </c>
+      <c r="C565" t="n">
+        <v>0</v>
+      </c>
+      <c r="D565" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B566" s="22" t="n">
+        <v>39355</v>
+      </c>
+      <c r="C566" t="n">
+        <v>0</v>
+      </c>
+      <c r="D566" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B567" s="22" t="n">
+        <v>39537</v>
+      </c>
+      <c r="C567" t="n">
+        <v>0</v>
+      </c>
+      <c r="D567" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B568" s="22" t="n">
+        <v>39721</v>
+      </c>
+      <c r="C568" t="n">
+        <v>0</v>
+      </c>
+      <c r="D568" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B569" s="22" t="n">
+        <v>39902</v>
+      </c>
+      <c r="C569" t="n">
+        <v>0</v>
+      </c>
+      <c r="D569" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B570" s="22" t="n">
+        <v>40086</v>
+      </c>
+      <c r="C570" t="n">
+        <v>0</v>
+      </c>
+      <c r="D570" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B571" s="22" t="n">
+        <v>40267</v>
+      </c>
+      <c r="C571" t="n">
+        <v>0</v>
+      </c>
+      <c r="D571" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B572" s="22" t="n">
+        <v>40451</v>
+      </c>
+      <c r="C572" t="n">
+        <v>0</v>
+      </c>
+      <c r="D572" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B573" s="22" t="n">
+        <v>40632</v>
+      </c>
+      <c r="C573" t="n">
+        <v>0</v>
+      </c>
+      <c r="D573" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B574" s="22" t="n">
+        <v>40816</v>
+      </c>
+      <c r="C574" t="n">
+        <v>0</v>
+      </c>
+      <c r="D574" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B575" s="22" t="n">
+        <v>40998</v>
+      </c>
+      <c r="C575" t="n">
+        <v>0</v>
+      </c>
+      <c r="D575" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B576" s="22" t="n">
+        <v>41182</v>
+      </c>
+      <c r="C576" t="n">
+        <v>0</v>
+      </c>
+      <c r="D576" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B577" s="22" t="n">
+        <v>41363</v>
+      </c>
+      <c r="C577" t="n">
+        <v>0</v>
+      </c>
+      <c r="D577" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B578" s="22" t="n">
+        <v>41547</v>
+      </c>
+      <c r="C578" t="n">
+        <v>0</v>
+      </c>
+      <c r="D578" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B579" s="22" t="n">
+        <v>41728</v>
+      </c>
+      <c r="C579" t="n">
+        <v>0</v>
+      </c>
+      <c r="D579" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B580" s="22" t="n">
+        <v>41912</v>
+      </c>
+      <c r="C580" t="n">
+        <v>0</v>
+      </c>
+      <c r="D580" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B581" s="22" t="n">
+        <v>42093</v>
+      </c>
+      <c r="C581" t="n">
+        <v>0</v>
+      </c>
+      <c r="D581" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B582" s="22" t="n">
+        <v>42277</v>
+      </c>
+      <c r="C582" t="n">
+        <v>0</v>
+      </c>
+      <c r="D582" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B583" s="22" t="n">
+        <v>42459</v>
+      </c>
+      <c r="C583" t="n">
+        <v>0</v>
+      </c>
+      <c r="D583" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B584" s="22" t="n">
+        <v>42643</v>
+      </c>
+      <c r="C584" t="n">
+        <v>0</v>
+      </c>
+      <c r="D584" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B585" s="22" t="n">
+        <v>42824</v>
+      </c>
+      <c r="C585" t="n">
+        <v>0</v>
+      </c>
+      <c r="D585" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B586" s="22" t="n">
+        <v>43008</v>
+      </c>
+      <c r="C586" t="n">
+        <v>0</v>
+      </c>
+      <c r="D586" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B587" s="22" t="n">
+        <v>43189</v>
+      </c>
+      <c r="C587" t="n">
+        <v>0</v>
+      </c>
+      <c r="D587" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B588" s="22" t="n">
+        <v>43373</v>
+      </c>
+      <c r="C588" t="n">
+        <v>0</v>
+      </c>
+      <c r="D588" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B589" s="22" t="n">
+        <v>43554</v>
+      </c>
+      <c r="C589" t="n">
+        <v>0</v>
+      </c>
+      <c r="D589" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B590" s="22" t="n">
+        <v>43738</v>
+      </c>
+      <c r="C590" t="n">
+        <v>0</v>
+      </c>
+      <c r="D590" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B591" s="22" t="n">
+        <v>43920</v>
+      </c>
+      <c r="C591" t="n">
+        <v>0</v>
+      </c>
+      <c r="D591" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B592" s="22" t="n">
+        <v>44104</v>
+      </c>
+      <c r="C592" t="n">
+        <v>0</v>
+      </c>
+      <c r="D592" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B593" s="22" t="n">
+        <v>44285</v>
+      </c>
+      <c r="C593" t="n">
+        <v>0</v>
+      </c>
+      <c r="D593" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B594" s="22" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C594" t="n">
+        <v>0</v>
+      </c>
+      <c r="D594" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B595" s="22" t="n">
+        <v>44650</v>
+      </c>
+      <c r="C595" t="n">
+        <v>0</v>
+      </c>
+      <c r="D595" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B596" s="22" t="n">
+        <v>44834</v>
+      </c>
+      <c r="C596" t="n">
+        <v>0</v>
+      </c>
+      <c r="D596" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B597" s="22" t="n">
+        <v>45015</v>
+      </c>
+      <c r="C597" t="n">
+        <v>0</v>
+      </c>
+      <c r="D597" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B598" s="22" t="n">
+        <v>45199</v>
+      </c>
+      <c r="C598" t="n">
+        <v>0</v>
+      </c>
+      <c r="D598" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B599" s="22" t="n">
+        <v>45381</v>
+      </c>
+      <c r="C599" t="n">
+        <v>0</v>
+      </c>
+      <c r="D599" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B600" s="22" t="n">
+        <v>45565</v>
+      </c>
+      <c r="C600" t="n">
+        <v>0</v>
+      </c>
+      <c r="D600" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B601" s="22" t="n">
+        <v>45746</v>
+      </c>
+      <c r="C601" t="n">
+        <v>0</v>
+      </c>
+      <c r="D601" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B602" s="22" t="n">
+        <v>45930</v>
+      </c>
+      <c r="C602" t="n">
+        <v>0</v>
+      </c>
+      <c r="D602" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B603" s="22" t="n">
+        <v>46111</v>
+      </c>
+      <c r="C603" t="n">
+        <v>0</v>
+      </c>
+      <c r="D603" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B604" s="22" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C604" t="n">
+        <v>0</v>
+      </c>
+      <c r="D604" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B605" s="22" t="n">
+        <v>46476</v>
+      </c>
+      <c r="C605" t="n">
+        <v>0</v>
+      </c>
+      <c r="D605" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B606" s="22" t="n">
+        <v>46660</v>
+      </c>
+      <c r="C606" t="n">
+        <v>0</v>
+      </c>
+      <c r="D606" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B607" s="22" t="n">
+        <v>46842</v>
+      </c>
+      <c r="C607" t="n">
+        <v>0</v>
+      </c>
+      <c r="D607" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B608" s="22" t="n">
+        <v>47026</v>
+      </c>
+      <c r="C608" t="n">
+        <v>0</v>
+      </c>
+      <c r="D608" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B609" s="22" t="n">
+        <v>47207</v>
+      </c>
+      <c r="C609" t="n">
+        <v>0</v>
+      </c>
+      <c r="D609" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B610" s="22" t="n">
+        <v>47391</v>
+      </c>
+      <c r="C610" t="n">
+        <v>5</v>
+      </c>
+      <c r="D610" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B611" s="22" t="n">
+        <v>47572</v>
+      </c>
+      <c r="C611" t="n">
+        <v>5</v>
+      </c>
+      <c r="D611" t="n">
+        <v>0.84075</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B612" s="22" t="n">
+        <v>47756</v>
+      </c>
+      <c r="C612" t="n">
+        <v>5</v>
+      </c>
+      <c r="D612" t="n">
+        <v>0.7965</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B613" s="22" t="n">
+        <v>47937</v>
+      </c>
+      <c r="C613" t="n">
+        <v>5</v>
+      </c>
+      <c r="D613" t="n">
+        <v>0.75225</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B614" s="22" t="n">
+        <v>48121</v>
+      </c>
+      <c r="C614" t="n">
+        <v>5</v>
+      </c>
+      <c r="D614" t="n">
+        <v>0.708</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B615" s="22" t="n">
+        <v>48303</v>
+      </c>
+      <c r="C615" t="n">
+        <v>5</v>
+      </c>
+      <c r="D615" t="n">
+        <v>0.66375</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B616" s="22" t="n">
+        <v>48487</v>
+      </c>
+      <c r="C616" t="n">
+        <v>5</v>
+      </c>
+      <c r="D616" t="n">
+        <v>0.6195000000000001</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B617" s="22" t="n">
+        <v>48668</v>
+      </c>
+      <c r="C617" t="n">
+        <v>5</v>
+      </c>
+      <c r="D617" t="n">
+        <v>0.57525</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B618" s="22" t="n">
+        <v>48852</v>
+      </c>
+      <c r="C618" t="n">
+        <v>5</v>
+      </c>
+      <c r="D618" t="n">
+        <v>0.531</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B619" s="22" t="n">
+        <v>49033</v>
+      </c>
+      <c r="C619" t="n">
+        <v>5</v>
+      </c>
+      <c r="D619" t="n">
+        <v>0.48675</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B620" s="22" t="n">
+        <v>49217</v>
+      </c>
+      <c r="C620" t="n">
+        <v>5</v>
+      </c>
+      <c r="D620" t="n">
+        <v>0.4425</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B621" s="22" t="n">
+        <v>49398</v>
+      </c>
+      <c r="C621" t="n">
+        <v>5</v>
+      </c>
+      <c r="D621" t="n">
+        <v>0.39825</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B622" s="22" t="n">
+        <v>49582</v>
+      </c>
+      <c r="C622" t="n">
+        <v>5</v>
+      </c>
+      <c r="D622" t="n">
+        <v>0.354</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B623" s="22" t="n">
+        <v>49764</v>
+      </c>
+      <c r="C623" t="n">
+        <v>5</v>
+      </c>
+      <c r="D623" t="n">
+        <v>0.30975</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B624" s="22" t="n">
+        <v>49948</v>
+      </c>
+      <c r="C624" t="n">
+        <v>5</v>
+      </c>
+      <c r="D624" t="n">
+        <v>0.2655</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B625" s="22" t="n">
+        <v>50129</v>
+      </c>
+      <c r="C625" t="n">
+        <v>5</v>
+      </c>
+      <c r="D625" t="n">
+        <v>0.22125</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B626" s="22" t="n">
+        <v>50313</v>
+      </c>
+      <c r="C626" t="n">
+        <v>5</v>
+      </c>
+      <c r="D626" t="n">
+        <v>0.177</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B627" s="22" t="n">
+        <v>50494</v>
+      </c>
+      <c r="C627" t="n">
+        <v>5</v>
+      </c>
+      <c r="D627" t="n">
+        <v>0.13275</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>PARP</t>
+        </is>
+      </c>
+      <c r="B628" s="22" t="n">
+        <v>50770</v>
+      </c>
+      <c r="C628" t="n">
+        <v>10</v>
+      </c>
+      <c r="D628" t="n">
+        <v>0.0885</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B629" s="22" t="n">
+        <v>38076</v>
+      </c>
+      <c r="C629" t="n">
+        <v>0</v>
+      </c>
+      <c r="D629" t="n">
+        <v>0.4425</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B630" s="22" t="n">
+        <v>38260</v>
+      </c>
+      <c r="C630" t="n">
+        <v>0</v>
+      </c>
+      <c r="D630" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B631" s="22" t="n">
+        <v>38441</v>
+      </c>
+      <c r="C631" t="n">
+        <v>0</v>
+      </c>
+      <c r="D631" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B632" s="22" t="n">
+        <v>38625</v>
+      </c>
+      <c r="C632" t="n">
+        <v>0</v>
+      </c>
+      <c r="D632" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B633" s="22" t="n">
+        <v>38806</v>
+      </c>
+      <c r="C633" t="n">
+        <v>0</v>
+      </c>
+      <c r="D633" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B634" s="22" t="n">
+        <v>38990</v>
+      </c>
+      <c r="C634" t="n">
+        <v>0</v>
+      </c>
+      <c r="D634" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B635" s="22" t="n">
+        <v>39171</v>
+      </c>
+      <c r="C635" t="n">
+        <v>0</v>
+      </c>
+      <c r="D635" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B636" s="22" t="n">
+        <v>39355</v>
+      </c>
+      <c r="C636" t="n">
+        <v>0</v>
+      </c>
+      <c r="D636" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B637" s="22" t="n">
+        <v>39537</v>
+      </c>
+      <c r="C637" t="n">
+        <v>0</v>
+      </c>
+      <c r="D637" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B638" s="22" t="n">
+        <v>39721</v>
+      </c>
+      <c r="C638" t="n">
+        <v>0</v>
+      </c>
+      <c r="D638" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B639" s="22" t="n">
+        <v>39902</v>
+      </c>
+      <c r="C639" t="n">
+        <v>0</v>
+      </c>
+      <c r="D639" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B640" s="22" t="n">
+        <v>40086</v>
+      </c>
+      <c r="C640" t="n">
+        <v>0</v>
+      </c>
+      <c r="D640" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B641" s="22" t="n">
+        <v>40267</v>
+      </c>
+      <c r="C641" t="n">
+        <v>0</v>
+      </c>
+      <c r="D641" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B642" s="22" t="n">
+        <v>40451</v>
+      </c>
+      <c r="C642" t="n">
+        <v>0</v>
+      </c>
+      <c r="D642" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B643" s="22" t="n">
+        <v>40632</v>
+      </c>
+      <c r="C643" t="n">
+        <v>0</v>
+      </c>
+      <c r="D643" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B644" s="22" t="n">
+        <v>40816</v>
+      </c>
+      <c r="C644" t="n">
+        <v>0</v>
+      </c>
+      <c r="D644" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B645" s="22" t="n">
+        <v>40998</v>
+      </c>
+      <c r="C645" t="n">
+        <v>0</v>
+      </c>
+      <c r="D645" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B646" s="22" t="n">
+        <v>41182</v>
+      </c>
+      <c r="C646" t="n">
+        <v>0</v>
+      </c>
+      <c r="D646" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B647" s="22" t="n">
+        <v>41363</v>
+      </c>
+      <c r="C647" t="n">
+        <v>0</v>
+      </c>
+      <c r="D647" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B648" s="22" t="n">
+        <v>41547</v>
+      </c>
+      <c r="C648" t="n">
+        <v>0</v>
+      </c>
+      <c r="D648" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B649" s="22" t="n">
+        <v>41728</v>
+      </c>
+      <c r="C649" t="n">
+        <v>0</v>
+      </c>
+      <c r="D649" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B650" s="22" t="n">
+        <v>41912</v>
+      </c>
+      <c r="C650" t="n">
+        <v>0</v>
+      </c>
+      <c r="D650" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B651" s="22" t="n">
+        <v>42093</v>
+      </c>
+      <c r="C651" t="n">
+        <v>0</v>
+      </c>
+      <c r="D651" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B652" s="22" t="n">
+        <v>42277</v>
+      </c>
+      <c r="C652" t="n">
+        <v>0</v>
+      </c>
+      <c r="D652" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B653" s="22" t="n">
+        <v>42459</v>
+      </c>
+      <c r="C653" t="n">
+        <v>0</v>
+      </c>
+      <c r="D653" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B654" s="22" t="n">
+        <v>42643</v>
+      </c>
+      <c r="C654" t="n">
+        <v>0</v>
+      </c>
+      <c r="D654" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B655" s="22" t="n">
+        <v>42824</v>
+      </c>
+      <c r="C655" t="n">
+        <v>0</v>
+      </c>
+      <c r="D655" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B656" s="22" t="n">
+        <v>43008</v>
+      </c>
+      <c r="C656" t="n">
+        <v>0</v>
+      </c>
+      <c r="D656" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B657" s="22" t="n">
+        <v>43189</v>
+      </c>
+      <c r="C657" t="n">
+        <v>0</v>
+      </c>
+      <c r="D657" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B658" s="22" t="n">
+        <v>43373</v>
+      </c>
+      <c r="C658" t="n">
+        <v>0</v>
+      </c>
+      <c r="D658" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B659" s="22" t="n">
+        <v>43554</v>
+      </c>
+      <c r="C659" t="n">
+        <v>0</v>
+      </c>
+      <c r="D659" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B660" s="22" t="n">
+        <v>43738</v>
+      </c>
+      <c r="C660" t="n">
+        <v>0</v>
+      </c>
+      <c r="D660" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B661" s="22" t="n">
+        <v>43920</v>
+      </c>
+      <c r="C661" t="n">
+        <v>0</v>
+      </c>
+      <c r="D661" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B662" s="22" t="n">
+        <v>44104</v>
+      </c>
+      <c r="C662" t="n">
+        <v>0</v>
+      </c>
+      <c r="D662" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B663" s="22" t="n">
+        <v>44285</v>
+      </c>
+      <c r="C663" t="n">
+        <v>0</v>
+      </c>
+      <c r="D663" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B664" s="22" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C664" t="n">
+        <v>0</v>
+      </c>
+      <c r="D664" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B665" s="22" t="n">
+        <v>44650</v>
+      </c>
+      <c r="C665" t="n">
+        <v>0</v>
+      </c>
+      <c r="D665" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B666" s="22" t="n">
+        <v>44834</v>
+      </c>
+      <c r="C666" t="n">
+        <v>0</v>
+      </c>
+      <c r="D666" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B667" s="22" t="n">
+        <v>45015</v>
+      </c>
+      <c r="C667" t="n">
+        <v>0</v>
+      </c>
+      <c r="D667" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B668" s="22" t="n">
+        <v>45199</v>
+      </c>
+      <c r="C668" t="n">
+        <v>0</v>
+      </c>
+      <c r="D668" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B669" s="22" t="n">
+        <v>45381</v>
+      </c>
+      <c r="C669" t="n">
+        <v>0</v>
+      </c>
+      <c r="D669" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B670" s="22" t="n">
+        <v>45565</v>
+      </c>
+      <c r="C670" t="n">
+        <v>0</v>
+      </c>
+      <c r="D670" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B671" s="22" t="n">
+        <v>45746</v>
+      </c>
+      <c r="C671" t="n">
+        <v>0</v>
+      </c>
+      <c r="D671" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B672" s="22" t="n">
+        <v>45930</v>
+      </c>
+      <c r="C672" t="n">
+        <v>0</v>
+      </c>
+      <c r="D672" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B673" s="22" t="n">
+        <v>46111</v>
+      </c>
+      <c r="C673" t="n">
+        <v>0</v>
+      </c>
+      <c r="D673" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B674" s="22" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C674" t="n">
+        <v>0</v>
+      </c>
+      <c r="D674" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B675" s="22" t="n">
+        <v>46476</v>
+      </c>
+      <c r="C675" t="n">
+        <v>0</v>
+      </c>
+      <c r="D675" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B676" s="22" t="n">
+        <v>46660</v>
+      </c>
+      <c r="C676" t="n">
+        <v>0</v>
+      </c>
+      <c r="D676" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B677" s="22" t="n">
+        <v>46842</v>
+      </c>
+      <c r="C677" t="n">
+        <v>0</v>
+      </c>
+      <c r="D677" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B678" s="22" t="n">
+        <v>47026</v>
+      </c>
+      <c r="C678" t="n">
+        <v>0</v>
+      </c>
+      <c r="D678" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B679" s="22" t="n">
+        <v>47207</v>
+      </c>
+      <c r="C679" t="n">
+        <v>0</v>
+      </c>
+      <c r="D679" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B680" s="22" t="n">
+        <v>47391</v>
+      </c>
+      <c r="C680" t="n">
+        <v>5</v>
+      </c>
+      <c r="D680" t="n">
+        <v>0.885</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B681" s="22" t="n">
+        <v>47572</v>
+      </c>
+      <c r="C681" t="n">
+        <v>5</v>
+      </c>
+      <c r="D681" t="n">
+        <v>0.84075</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B682" s="22" t="n">
+        <v>47756</v>
+      </c>
+      <c r="C682" t="n">
+        <v>5</v>
+      </c>
+      <c r="D682" t="n">
+        <v>0.7965</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B683" s="22" t="n">
+        <v>47937</v>
+      </c>
+      <c r="C683" t="n">
+        <v>5</v>
+      </c>
+      <c r="D683" t="n">
+        <v>0.75225</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B684" s="22" t="n">
+        <v>48121</v>
+      </c>
+      <c r="C684" t="n">
+        <v>5</v>
+      </c>
+      <c r="D684" t="n">
+        <v>0.708</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B685" s="22" t="n">
+        <v>48303</v>
+      </c>
+      <c r="C685" t="n">
+        <v>5</v>
+      </c>
+      <c r="D685" t="n">
+        <v>0.66375</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B686" s="22" t="n">
+        <v>48487</v>
+      </c>
+      <c r="C686" t="n">
+        <v>5</v>
+      </c>
+      <c r="D686" t="n">
+        <v>0.6195000000000001</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B687" s="22" t="n">
+        <v>48668</v>
+      </c>
+      <c r="C687" t="n">
+        <v>5</v>
+      </c>
+      <c r="D687" t="n">
+        <v>0.57525</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B688" s="22" t="n">
+        <v>48852</v>
+      </c>
+      <c r="C688" t="n">
+        <v>5</v>
+      </c>
+      <c r="D688" t="n">
+        <v>0.531</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B689" s="22" t="n">
+        <v>49033</v>
+      </c>
+      <c r="C689" t="n">
+        <v>5</v>
+      </c>
+      <c r="D689" t="n">
+        <v>0.48675</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B690" s="22" t="n">
+        <v>49217</v>
+      </c>
+      <c r="C690" t="n">
+        <v>5</v>
+      </c>
+      <c r="D690" t="n">
+        <v>0.4425</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B691" s="22" t="n">
+        <v>49398</v>
+      </c>
+      <c r="C691" t="n">
+        <v>5</v>
+      </c>
+      <c r="D691" t="n">
+        <v>0.39825</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B692" s="22" t="n">
+        <v>49582</v>
+      </c>
+      <c r="C692" t="n">
+        <v>5</v>
+      </c>
+      <c r="D692" t="n">
+        <v>0.354</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B693" s="22" t="n">
+        <v>49764</v>
+      </c>
+      <c r="C693" t="n">
+        <v>5</v>
+      </c>
+      <c r="D693" t="n">
+        <v>0.30975</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B694" s="22" t="n">
+        <v>49948</v>
+      </c>
+      <c r="C694" t="n">
+        <v>5</v>
+      </c>
+      <c r="D694" t="n">
+        <v>0.2655</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B695" s="22" t="n">
+        <v>50129</v>
+      </c>
+      <c r="C695" t="n">
+        <v>5</v>
+      </c>
+      <c r="D695" t="n">
+        <v>0.22125</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B696" s="22" t="n">
+        <v>50313</v>
+      </c>
+      <c r="C696" t="n">
+        <v>5</v>
+      </c>
+      <c r="D696" t="n">
+        <v>0.177</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B697" s="22" t="n">
+        <v>50494</v>
+      </c>
+      <c r="C697" t="n">
+        <v>5</v>
+      </c>
+      <c r="D697" t="n">
+        <v>0.13275</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>PAP0</t>
+        </is>
+      </c>
+      <c r="B698" s="22" t="n">
+        <v>50770</v>
+      </c>
+      <c r="C698" t="n">
+        <v>10</v>
+      </c>
+      <c r="D698" t="n">
+        <v>0.0885</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>TZV26</t>
+        </is>
+      </c>
+      <c r="B699" s="22" t="n">
+        <v>45656</v>
+      </c>
+      <c r="C699" t="n">
+        <v>0</v>
+      </c>
+      <c r="D699" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>TZV26</t>
+        </is>
+      </c>
+      <c r="B700" s="22" t="n">
+        <v>45838</v>
+      </c>
+      <c r="C700" t="n">
+        <v>0</v>
+      </c>
+      <c r="D700" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>TZV26</t>
+        </is>
+      </c>
+      <c r="B701" s="22" t="n">
+        <v>46021</v>
+      </c>
+      <c r="C701" t="n">
+        <v>0</v>
+      </c>
+      <c r="D701" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>TZV26</t>
+        </is>
+      </c>
+      <c r="B702" s="22" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C702" t="n">
+        <v>100</v>
+      </c>
+      <c r="D702" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>D30S6</t>
+        </is>
+      </c>
+      <c r="B703" s="22" t="n">
+        <v>45746</v>
+      </c>
+      <c r="C703" t="n">
+        <v>0</v>
+      </c>
+      <c r="D703" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>D30S6</t>
+        </is>
+      </c>
+      <c r="B704" s="22" t="n">
+        <v>45930</v>
+      </c>
+      <c r="C704" t="n">
+        <v>0</v>
+      </c>
+      <c r="D704" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>D30S6</t>
+        </is>
+      </c>
+      <c r="B705" s="22" t="n">
+        <v>46111</v>
+      </c>
+      <c r="C705" t="n">
+        <v>0</v>
+      </c>
+      <c r="D705" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>D30S6</t>
+        </is>
+      </c>
+      <c r="B706" s="22" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C706" t="n">
+        <v>100</v>
+      </c>
+      <c r="D706" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>TZV27</t>
+        </is>
+      </c>
+      <c r="B707" s="22" t="n">
+        <v>46021</v>
+      </c>
+      <c r="C707" t="n">
+        <v>0</v>
+      </c>
+      <c r="D707" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>TZV27</t>
+        </is>
+      </c>
+      <c r="B708" s="22" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C708" t="n">
+        <v>0</v>
+      </c>
+      <c r="D708" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>TZV27</t>
+        </is>
+      </c>
+      <c r="B709" s="22" t="n">
+        <v>46386</v>
+      </c>
+      <c r="C709" t="n">
+        <v>0</v>
+      </c>
+      <c r="D709" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>TZV27</t>
+        </is>
+      </c>
+      <c r="B710" s="22" t="n">
+        <v>46568</v>
+      </c>
+      <c r="C710" t="n">
+        <v>100</v>
+      </c>
+      <c r="D710" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>TZV28</t>
+        </is>
+      </c>
+      <c r="B711" s="22" t="n">
+        <v>46386</v>
+      </c>
+      <c r="C711" t="n">
+        <v>0</v>
+      </c>
+      <c r="D711" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>TZV28</t>
+        </is>
+      </c>
+      <c r="B712" s="22" t="n">
+        <v>46568</v>
+      </c>
+      <c r="C712" t="n">
+        <v>0</v>
+      </c>
+      <c r="D712" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>TZV28</t>
+        </is>
+      </c>
+      <c r="B713" s="22" t="n">
+        <v>46751</v>
+      </c>
+      <c r="C713" t="n">
+        <v>0</v>
+      </c>
+      <c r="D713" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>TZV28</t>
+        </is>
+      </c>
+      <c r="B714" s="22" t="n">
+        <v>46934</v>
+      </c>
+      <c r="C714" t="n">
+        <v>100</v>
+      </c>
+      <c r="D714" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
